--- a/backend/DATA_ALL.xlsx
+++ b/backend/DATA_ALL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vonje\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFA2B7E-74F1-4A53-A5F7-144301181433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F989C7AE-C570-4DC4-908B-1E78CBFBE545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA_ALL" sheetId="6" r:id="rId1"/>
@@ -3486,6 +3486,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF5B3F86"/>
@@ -3520,1736 +3544,1736 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5288,728 +5312,728 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6048,200 +6072,200 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6280,744 +6304,744 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7056,408 +7080,408 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7477,37 +7501,13 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="388">
     <tableStyle name="SURVEY RESULTS-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="784"/>
-      <tableStyleElement type="headerRow" dxfId="787"/>
-      <tableStyleElement type="firstRowStripe" dxfId="786"/>
-      <tableStyleElement type="secondRowStripe" dxfId="785"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="787"/>
+      <tableStyleElement type="headerRow" dxfId="786"/>
+      <tableStyleElement type="firstRowStripe" dxfId="785"/>
+      <tableStyleElement type="secondRowStripe" dxfId="784"/>
     </tableStyle>
     <tableStyle name="2022 -2025 PRC DATA RECORD-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="783"/>
@@ -7610,10 +7610,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="734"/>
     </tableStyle>
     <tableStyle name="DATA_MODEL-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF1A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="730"/>
-      <tableStyleElement type="headerRow" dxfId="733"/>
-      <tableStyleElement type="firstRowStripe" dxfId="732"/>
-      <tableStyleElement type="secondRowStripe" dxfId="731"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="733"/>
+      <tableStyleElement type="headerRow" dxfId="732"/>
+      <tableStyleElement type="firstRowStripe" dxfId="731"/>
+      <tableStyleElement type="secondRowStripe" dxfId="730"/>
     </tableStyle>
     <tableStyle name="DATA_MODEL-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF1B000000}">
       <tableStyleElement type="firstRowStripe" dxfId="729"/>
@@ -7800,10 +7800,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="638"/>
     </tableStyle>
     <tableStyle name="DATA_EVALUATION-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF49000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="634"/>
-      <tableStyleElement type="headerRow" dxfId="637"/>
-      <tableStyleElement type="firstRowStripe" dxfId="636"/>
-      <tableStyleElement type="secondRowStripe" dxfId="635"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="637"/>
+      <tableStyleElement type="headerRow" dxfId="636"/>
+      <tableStyleElement type="firstRowStripe" dxfId="635"/>
+      <tableStyleElement type="secondRowStripe" dxfId="634"/>
     </tableStyle>
     <tableStyle name="DATA_EVALUATION-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF4A000000}">
       <tableStyleElement type="firstRowStripe" dxfId="633"/>
@@ -7854,10 +7854,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="610"/>
     </tableStyle>
     <tableStyle name="DATA_ALL1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF56000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="606"/>
-      <tableStyleElement type="headerRow" dxfId="609"/>
-      <tableStyleElement type="firstRowStripe" dxfId="608"/>
-      <tableStyleElement type="secondRowStripe" dxfId="607"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="609"/>
+      <tableStyleElement type="headerRow" dxfId="608"/>
+      <tableStyleElement type="firstRowStripe" dxfId="607"/>
+      <tableStyleElement type="secondRowStripe" dxfId="606"/>
     </tableStyle>
     <tableStyle name="DATA_ALL1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF57000000}">
       <tableStyleElement type="firstRowStripe" dxfId="605"/>
@@ -8040,10 +8040,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="516"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (EVALUATION)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF84000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="512"/>
-      <tableStyleElement type="headerRow" dxfId="515"/>
-      <tableStyleElement type="firstRowStripe" dxfId="514"/>
-      <tableStyleElement type="secondRowStripe" dxfId="513"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="515"/>
+      <tableStyleElement type="headerRow" dxfId="514"/>
+      <tableStyleElement type="firstRowStripe" dxfId="513"/>
+      <tableStyleElement type="secondRowStripe" dxfId="512"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (EVALUATION)-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF85000000}">
       <tableStyleElement type="firstRowStripe" dxfId="511"/>
@@ -8478,10 +8478,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="296"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (MODEL)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFFF1000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="292"/>
-      <tableStyleElement type="headerRow" dxfId="295"/>
-      <tableStyleElement type="firstRowStripe" dxfId="294"/>
-      <tableStyleElement type="secondRowStripe" dxfId="293"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="295"/>
+      <tableStyleElement type="headerRow" dxfId="294"/>
+      <tableStyleElement type="firstRowStripe" dxfId="293"/>
+      <tableStyleElement type="secondRowStripe" dxfId="292"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (MODEL)-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFFF2000000}">
       <tableStyleElement type="firstRowStripe" dxfId="291"/>
@@ -9362,23 +9362,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:CT160"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:98" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>93</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>89</v>
@@ -9663,7 +9663,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>115</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>99</v>
       </c>
@@ -10235,7 +10235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>39</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>52</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>62</v>
       </c>
@@ -11383,7 +11383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>114</v>
       </c>
@@ -11669,7 +11669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>227</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>125</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>128</v>
       </c>
@@ -12521,7 +12521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>129</v>
       </c>
@@ -12805,7 +12805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>130</v>
       </c>
@@ -13093,7 +13093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>131</v>
       </c>
@@ -13377,7 +13377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>228</v>
       </c>
@@ -13665,7 +13665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>229</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>132</v>
       </c>
@@ -14233,7 +14233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>133</v>
       </c>
@@ -14517,7 +14517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>134</v>
       </c>
@@ -14805,7 +14805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>68</v>
       </c>
@@ -15091,7 +15091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>73</v>
       </c>
@@ -15375,7 +15375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>77</v>
       </c>
@@ -15659,7 +15659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>79</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>136</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>137</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>138</v>
       </c>
@@ -16807,7 +16807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>139</v>
       </c>
@@ -17095,7 +17095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>140</v>
       </c>
@@ -17379,7 +17379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>141</v>
       </c>
@@ -17665,7 +17665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>142</v>
       </c>
@@ -17955,7 +17955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>145</v>
       </c>
@@ -18239,7 +18239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>151</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>153</v>
       </c>
@@ -18809,7 +18809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>154</v>
       </c>
@@ -19093,7 +19093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>155</v>
       </c>
@@ -19377,7 +19377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>156</v>
       </c>
@@ -19667,7 +19667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>159</v>
       </c>
@@ -19949,7 +19949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>160</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>231</v>
       </c>
@@ -20519,7 +20519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>165</v>
       </c>
@@ -20809,7 +20809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>169</v>
       </c>
@@ -21093,7 +21093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>170</v>
       </c>
@@ -21377,7 +21377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>171</v>
       </c>
@@ -21665,7 +21665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>172</v>
       </c>
@@ -21947,7 +21947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>173</v>
       </c>
@@ -22231,7 +22231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>184</v>
       </c>
@@ -22525,7 +22525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>233</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>234</v>
       </c>
@@ -23109,7 +23109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>136</v>
       </c>
@@ -23395,7 +23395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>135</v>
       </c>
@@ -23683,7 +23683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>235</v>
       </c>
@@ -23973,7 +23973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>85</v>
       </c>
@@ -24261,7 +24261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>236</v>
       </c>
@@ -24547,7 +24547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>237</v>
       </c>
@@ -24839,7 +24839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>185</v>
       </c>
@@ -25125,7 +25125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>238</v>
       </c>
@@ -25415,7 +25415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>237</v>
       </c>
@@ -25703,7 +25703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>180</v>
       </c>
@@ -25991,7 +25991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>187</v>
       </c>
@@ -26277,7 +26277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>193</v>
       </c>
@@ -26559,7 +26559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>194</v>
       </c>
@@ -26845,7 +26845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>195</v>
       </c>
@@ -27135,7 +27135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>196</v>
       </c>
@@ -27421,7 +27421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>143</v>
       </c>
@@ -27705,7 +27705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>144</v>
       </c>
@@ -27989,7 +27989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>240</v>
       </c>
@@ -28273,7 +28273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>147</v>
       </c>
@@ -28555,7 +28555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>149</v>
       </c>
@@ -28837,7 +28837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>150</v>
       </c>
@@ -29121,7 +29121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>152</v>
       </c>
@@ -29405,7 +29405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>175</v>
       </c>
@@ -29689,7 +29689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>185</v>
       </c>
@@ -29979,7 +29979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>176</v>
       </c>
@@ -30261,7 +30261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>178</v>
       </c>
@@ -30543,7 +30543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>174</v>
       </c>
@@ -30825,7 +30825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>161</v>
       </c>
@@ -31111,7 +31111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>186</v>
       </c>
@@ -31393,7 +31393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>242</v>
       </c>
@@ -31677,7 +31677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>188</v>
       </c>
@@ -31959,7 +31959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>189</v>
       </c>
@@ -32241,7 +32241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>243</v>
       </c>
@@ -32525,7 +32525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>190</v>
       </c>
@@ -32815,7 +32815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>191</v>
       </c>
@@ -33099,7 +33099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>192</v>
       </c>
@@ -33391,7 +33391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>126</v>
       </c>
@@ -33679,7 +33679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>127</v>
       </c>
@@ -33965,7 +33965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>162</v>
       </c>
@@ -34247,7 +34247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>163</v>
       </c>
@@ -34529,7 +34529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>248</v>
       </c>
@@ -34813,7 +34813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>164</v>
       </c>
@@ -35095,7 +35095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>179</v>
       </c>
@@ -35377,7 +35377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>166</v>
       </c>
@@ -35659,7 +35659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>167</v>
       </c>
@@ -35945,7 +35945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>168</v>
       </c>
@@ -36227,7 +36227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>177</v>
       </c>
@@ -36509,7 +36509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>249</v>
       </c>
@@ -36791,7 +36791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>101</v>
       </c>
@@ -37085,7 +37085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>102</v>
       </c>
@@ -37369,7 +37369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>103</v>
       </c>
@@ -37651,7 +37651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>104</v>
       </c>
@@ -37933,7 +37933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>105</v>
       </c>
@@ -38227,7 +38227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>106</v>
       </c>
@@ -38509,7 +38509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>107</v>
       </c>
@@ -38791,7 +38791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>157</v>
       </c>
@@ -39075,7 +39075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>116</v>
       </c>
@@ -39361,7 +39361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>117</v>
       </c>
@@ -39645,7 +39645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>118</v>
       </c>
@@ -39929,7 +39929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
         <v>119</v>
       </c>
@@ -40213,7 +40213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>120</v>
       </c>
@@ -40507,7 +40507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>121</v>
       </c>
@@ -40791,7 +40791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>122</v>
       </c>
@@ -41079,7 +41079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>123</v>
       </c>
@@ -41363,7 +41363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>124</v>
       </c>
@@ -41649,7 +41649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
         <v>158</v>
       </c>
@@ -41931,7 +41931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>146</v>
       </c>
@@ -42213,7 +42213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>256</v>
       </c>
@@ -42495,7 +42495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>148</v>
       </c>
@@ -42777,7 +42777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>181</v>
       </c>
@@ -43063,7 +43063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>182</v>
       </c>
@@ -43347,7 +43347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>109</v>
       </c>
@@ -43631,7 +43631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>110</v>
       </c>
@@ -43917,7 +43917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
         <v>111</v>
       </c>
@@ -44199,7 +44199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>112</v>
       </c>
@@ -44485,7 +44485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>113</v>
       </c>
@@ -44771,7 +44771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>187</v>
       </c>
@@ -45057,7 +45057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>193</v>
       </c>
@@ -45339,7 +45339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>194</v>
       </c>
@@ -45625,7 +45625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>195</v>
       </c>
@@ -45915,7 +45915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>196</v>
       </c>
@@ -46201,7 +46201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>197</v>
       </c>
@@ -46483,7 +46483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>198</v>
       </c>
@@ -46765,7 +46765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
         <v>199</v>
       </c>
@@ -47047,7 +47047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>200</v>
       </c>
@@ -47329,7 +47329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>201</v>
       </c>
@@ -47617,7 +47617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>202</v>
       </c>
@@ -47899,7 +47899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>203</v>
       </c>
@@ -48181,7 +48181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>204</v>
       </c>
@@ -48463,7 +48463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>205</v>
       </c>
@@ -48745,7 +48745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>206</v>
       </c>
@@ -49027,7 +49027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>207</v>
       </c>
@@ -49313,7 +49313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>212</v>
       </c>
@@ -49601,7 +49601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
         <v>180</v>
       </c>
@@ -49889,7 +49889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>210</v>
       </c>
@@ -50177,7 +50177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>208</v>
       </c>
@@ -50463,7 +50463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>211</v>
       </c>
@@ -50747,7 +50747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>214</v>
       </c>
@@ -51031,7 +51031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>220</v>
       </c>
@@ -51315,7 +51315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
         <v>88</v>
       </c>
@@ -51597,7 +51597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>183</v>
       </c>
@@ -51891,7 +51891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>218</v>
       </c>
@@ -52183,7 +52183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
         <v>222</v>
       </c>
@@ -52467,7 +52467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
         <v>219</v>
       </c>
@@ -52753,7 +52753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
         <v>261</v>
       </c>
@@ -53035,7 +53035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>215</v>
       </c>
@@ -53321,7 +53321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>213</v>
       </c>
@@ -53613,7 +53613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>209</v>
       </c>
@@ -53895,7 +53895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
         <v>216</v>
       </c>
@@ -54179,7 +54179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
         <v>217</v>
       </c>
@@ -54463,7 +54463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
         <v>221</v>
       </c>
@@ -54757,7 +54757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
         <v>183</v>
       </c>

--- a/backend/DATA_ALL.xlsx
+++ b/backend/DATA_ALL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F989C7AE-C570-4DC4-908B-1E78CBFBE545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF70248-AF76-4E31-BD93-F8AC1C90FEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="DATA_ALL" sheetId="6" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -9372,13 +9373,13 @@
         <v>93</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>89</v>

--- a/backend/DATA_ALL.xlsx
+++ b/backend/DATA_ALL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF70248-AF76-4E31-BD93-F8AC1C90FEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA3A004-FAFF-4BC0-86B3-4AFFFB647AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9373,13 +9373,13 @@
         <v>93</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>89</v>

--- a/backend/DATA_ALL.xlsx
+++ b/backend/DATA_ALL.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA3A004-FAFF-4BC0-86B3-4AFFFB647AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EAC3E7-5033-4072-9DBD-5BBED17E8302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="1935" windowWidth="22845" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA_ALL" sheetId="6" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -9373,13 +9372,13 @@
         <v>93</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>89</v>
